--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A13522-CA5A-45C9-BFEB-8A00442B00F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0848CA92-6DAB-412E-8393-1A41D7DCB8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="116">
   <si>
     <t>##var</t>
   </si>
@@ -287,10 +287,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>胜利</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Victory</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -478,6 +474,22 @@
   </si>
   <si>
     <t>Find {0} commonly‑used Chinese characters</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡胜利</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_share</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>分享</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Share</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1155,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1412,197 +1424,208 @@
         <v>61</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="E19" t="s">
         <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>75</v>
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>88</v>
-      </c>
       <c r="E29" s="7" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B34" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>111</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0848CA92-6DAB-412E-8393-1A41D7DCB8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAAA0C1-2BE3-4462-BC9C-A873873DB96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="119">
   <si>
     <t>##var</t>
   </si>
@@ -490,6 +490,18 @@
   </si>
   <si>
     <t>Share</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_reward</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>REWARD</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1167,7 +1179,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA34"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1421,210 +1433,221 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D20" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E20" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B35" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D35" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E35" s="7" t="s">
         <v>111</v>
       </c>
     </row>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAAA0C1-2BE3-4462-BC9C-A873873DB96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C045DDAA-F10E-4DD6-A722-886278E324D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="122">
   <si>
     <t>##var</t>
   </si>
@@ -502,6 +502,18 @@
   </si>
   <si>
     <t>REWARD</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>home_social</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>社交</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Social</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1179,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1378,276 +1390,287 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>117</v>
+        <v>56</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>62</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B21" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B36" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D36" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>111</v>
       </c>
     </row>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C045DDAA-F10E-4DD6-A722-886278E324D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B28D11-9BFA-454C-8777-32F77B4781E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32250" yWindow="2505" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -514,6 +514,78 @@
   </si>
   <si>
     <t>Social</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide_step1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>再点亮这一笔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light up this stroke too</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide_step2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>点亮这一笔，找出第一个字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light up this stroke and find the first character</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide_step3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>再试一次，点亮这一笔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Try again—light up this stroke</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide_step4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>点「提交」，看看你找到了什么</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tap “Submit” to see what you found</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide_step5</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>You found it! Tap “Submit”</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>guide_step6</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>接下来，看你自己的啦！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Now it’s your turn!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>找到了！点「提交」</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1191,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1674,6 +1746,72 @@
         <v>111</v>
       </c>
     </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B37" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B38" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B39" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B40" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B41" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B42" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B28D11-9BFA-454C-8777-32F77B4781E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B66B41-AE41-4ABC-B05E-5C85DB8FAC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="165">
   <si>
     <t>##var</t>
   </si>
@@ -473,10 +473,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Find {0} commonly‑used Chinese characters</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>关卡胜利</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -587,6 +583,106 @@
   <si>
     <t>找到了！点「提交」</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>home_share</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>home_setting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setting</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_prop_next</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_prop_tip</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_prop_clear</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>清除</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_prop_select_all</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>全选</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Clear</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select All</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Find {0} commonly used Chinese characters</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_tips1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏未运行</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>未完成广告观看，请稍后重试</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game not running</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select stroke first</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Answer found already</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Invalid stroke combination</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ad view incomplete. Retry later</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>game_tips2</t>
+  </si>
+  <si>
+    <t>game_tips3</t>
+  </si>
+  <si>
+    <t>game_tips4</t>
+  </si>
+  <si>
+    <t>game_tips5</t>
   </si>
 </sst>
 </file>
@@ -1263,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1462,354 +1558,475 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>49</v>
+        <v>140</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B22" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B23" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E23" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
+      </c>
+      <c r="E24" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>85</v>
+        <v>78</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B38" s="7" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>129</v>
+        <v>40</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B43" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B44" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B45" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B46" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B47" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="E48" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>138</v>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B51" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B52" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B53" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B66B41-AE41-4ABC-B05E-5C85DB8FAC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8DDD80-FD96-460A-B5CF-36172A2E9277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="168">
   <si>
     <t>##var</t>
   </si>
@@ -683,6 +683,18 @@
   </si>
   <si>
     <t>game_tips5</t>
+  </si>
+  <si>
+    <t>setting_version</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version:{0}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前版本:{0}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1359,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -1646,386 +1658,397 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>62</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B24" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D24" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B38" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>41</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B46" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B47" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B48" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="7" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="7" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B51" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B52" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B53" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B54" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D54" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E54" s="7" t="s">
         <v>160</v>
       </c>
     </row>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -1371,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2525A7A-E1FA-4A3B-809C-FFEA7B53C7CA}">
-  <dimension ref="A1:AA54"/>
+  <dimension ref="A1:AA56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.875" bestFit="1" customWidth="1"/>
@@ -2052,6 +2052,40 @@
         <v>160</v>
       </c>
     </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>finish_double_reward</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>双倍奖励</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Double Rewards</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>finish_double_reward_claimed</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>已领取</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Claimed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8DDD80-FD96-460A-B5CF-36172A2E9277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6458403-2B59-49B3-86DC-89E3BCDB0F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="174">
   <si>
     <t>##var</t>
   </si>
@@ -208,9 +208,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>AlimamaFangYuanTiVF</t>
-  </si>
-  <si>
     <t>level_title</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -694,6 +691,28 @@
   </si>
   <si>
     <t>当前版本:{0}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>finish_double_reward</t>
+  </si>
+  <si>
+    <t>双倍奖励</t>
+  </si>
+  <si>
+    <t>Double Rewards</t>
+  </si>
+  <si>
+    <t>finish_double_reward_claimed</t>
+  </si>
+  <si>
+    <t>已领取</t>
+  </si>
+  <si>
+    <t>Claimed</t>
+  </si>
+  <si>
+    <t>TaiWanQuanZiKuZhengKaiTi-2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1335,7 +1354,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1356,7 +1375,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>42</v>
+        <v>173</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1559,337 +1578,337 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="E11" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>140</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>47</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="E20" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>61</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="E22" s="9" t="s">
         <v>113</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="E23" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="E24" t="s">
         <v>67</v>
-      </c>
-      <c r="E24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" t="s">
         <v>70</v>
-      </c>
-      <c r="E25" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="E26" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="E27" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="E28" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>85</v>
-      </c>
       <c r="E30" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D32" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>94</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>87</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="E36" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="E37" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B38" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="E38" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="E39" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>40</v>
@@ -1900,190 +1919,178 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="E41" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="E42" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="E43" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="E44" s="7" t="s">
         <v>122</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="E45" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B46" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="E46" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B47" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="E47" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B48" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="7" t="s">
         <v>133</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="7" t="s">
         <v>136</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>154</v>
-      </c>
       <c r="E50" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B51" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B52" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B53" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B54" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>finish_double_reward</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>双倍奖励</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>Double Rewards</t>
-        </is>
+      <c r="B55" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>finish_double_reward_claimed</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>已领取</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>Claimed</t>
-        </is>
+      <c r="B56" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6458403-2B59-49B3-86DC-89E3BCDB0F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F624B97-DC29-4E78-A3AA-103308D542CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="多语言|Language" sheetId="1" r:id="rId1"/>
@@ -212,14 +212,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>第{0}关 - {1}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level {0} - {1}</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>setting_title</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -713,6 +705,14 @@
   </si>
   <si>
     <t>TaiWanQuanZiKuZhengKaiTi-2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>第{0}关-{1}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level {0}-{1}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1354,7 +1354,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1581,334 +1581,334 @@
         <v>42</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>43</v>
+        <v>172</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>117</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>45</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>166</v>
-      </c>
       <c r="E19" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>114</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>111</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>62</v>
-      </c>
-      <c r="D23" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" t="s">
         <v>65</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
         <v>68</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>71</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="E34" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B35" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B36" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B38" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>40</v>
@@ -1919,178 +1919,178 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B45" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B46" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" s="7" t="s">
         <v>126</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B47" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E47" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B48" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>134</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B50" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D50" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B51" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B52" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B53" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B54" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B55" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>167</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B56" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E56" s="7" t="s">
         <v>170</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -1408,11 +1408,15 @@
       <x:c r="B12" s="9" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D12" s="9" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E12" s="9" t="s">
-        <x:v>51</x:v>
+      <x:c r="D12" s="9" t="inlineStr">
+        <x:is>
+          <x:t>考考好友</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Challenge Friends</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1518,11 +1522,15 @@
       <x:c r="B22" s="9" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D22" s="9" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E22" s="9" t="s">
-        <x:v>51</x:v>
+      <x:c r="D22" s="9" t="inlineStr">
+        <x:is>
+          <x:t>考考好友</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="9" t="inlineStr">
+        <x:is>
+          <x:t>Challenge Friends</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1918,11 +1926,15 @@
         <x:v>finish_share_title</x:v>
       </x:c>
       <x:c r="C58"/>
-      <x:c r="D58" s="7" t="str">
-        <x:v>我刚刚通过了第{0}关，来挑战一下吧！</x:v>
-      </x:c>
-      <x:c r="E58" s="7" t="str">
-        <x:v>I just cleared level {0}! Can you beat it?</x:v>
+      <x:c r="D58" s="7" t="inlineStr">
+        <x:is>
+          <x:t>我已通过第{0}关，考考你的眼力，看看你能闯到哪一关！</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E58" s="7" t="inlineStr">
+        <x:is>
+          <x:t>I cleared level {0}! How far can you get?</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>
